--- a/sld_components.xlsx
+++ b/sld_components.xlsx
@@ -9,10 +9,8 @@
   <sheets>
     <sheet name="Components" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Terminal Schedule" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Enclosure" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Additional Info" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Shop Drawing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Shop Drawing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,7 +53,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="007030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF8F00"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,25 +71,25 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="00FF0000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FF6600"/>
+      <color rgb="00ED7D31"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="007030A0"/>
+      <color rgb="0070AD47"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="002E75B6"/>
       <sz val="10"/>
     </font>
     <font>
@@ -94,7 +98,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -118,22 +122,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEEFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="002E4057"/>
       </patternFill>
     </fill>
   </fills>
@@ -212,66 +206,66 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -669,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -693,14 +687,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SLD Component Extraction  ·  xyz.dwg</t>
+          <t>SLD Component Extraction  ·  DB-B1.dwg</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Groups: 15   |   Total units: 38</t>
+          <t>Groups: 10   |   Total units: 42</t>
         </is>
       </c>
     </row>
@@ -792,12 +786,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>MCCB</t>
+          <t>SWITCH</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>MCCB 100AF</t>
+          <t>ISOL.S.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -807,17 +801,17 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>100A</t>
+          <t>40A</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>36kA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -832,16 +826,16 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>EDL-1 Input, EDL-2 Input</t>
+          <t>MAIN INCOMER</t>
         </is>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
@@ -860,7 +854,7 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Identified from text 'MCCB: AF=100A AT=100A' and '4x35mm2'. Feeds KWH meters.</t>
+          <t>Main switch 4x40A identified from clusters 019 and 020.</t>
         </is>
       </c>
     </row>
@@ -870,17 +864,17 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>METER</t>
+          <t>PILOT_LAMP</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>KWH Meter</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>3P</t>
+          <t>R/Y/B</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -915,11 +909,11 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Utility Metering</t>
+          <t>Phase Indication</t>
         </is>
       </c>
       <c r="L5" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -933,12 +927,12 @@
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>DXF_ONLY</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="P5" s="9" t="inlineStr">
         <is>
-          <t>Text 'KWH-1', 'KWH-2'.</t>
+          <t>Red/Green/Blue indicator lamps identified from DXF blocks.</t>
         </is>
       </c>
     </row>
@@ -948,17 +942,17 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>METER</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Phase Failure Relay</t>
+          <t>DIGITAL POWER METER</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3P</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -993,11 +987,11 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>EDL Protection</t>
+          <t>Panel Metering</t>
         </is>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
@@ -1006,17 +1000,17 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>DXF_ONLY</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Text 'PFR' near EDL inputs.</t>
+          <t>Digital power meter block and text clusters 021, 022.</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1020,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>CONTACTOR</t>
+          <t>SPD</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Contactor AC3</t>
+          <t>TYPE 2 / CLASS C</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1041,7 +1035,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>250A</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1061,7 +1055,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Up&lt;=1.2KV, 20KA Max</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1071,11 +1065,11 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>EDL Input Control, ATS-1, ATS-2, ATS-3 Switching</t>
+          <t>Surge Protection</t>
         </is>
       </c>
       <c r="L7" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
@@ -1084,7 +1078,7 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
@@ -1094,7 +1088,7 @@
       </c>
       <c r="P7" s="9" t="inlineStr">
         <is>
-          <t>Grouped 2x EDL contactors and 6x ATS contactors (C1/C2). Text 'CONTACTOR', 'C1 4x250A', 'C2 4x250A'.</t>
+          <t>SPD specs from clusters 064, 065, 068.</t>
         </is>
       </c>
     </row>
@@ -1102,34 +1096,34 @@
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>MCCB</t>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>FUSE_HOLDER</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>MCCB 250AF</t>
+          <t>gG</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>4P</t>
+          <t>3P</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>200A</t>
+          <t>32A</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>36kA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1144,12 +1138,12 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>ATS-1 Main Source Input</t>
+          <t>SPD protection</t>
         </is>
       </c>
       <c r="L8" s="4" t="n">
@@ -1172,7 +1166,7 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Downstream of EDL. Text 'MCCB: AF=250A AT=200A'. Feeds 'FROM EDL' line.</t>
+          <t>Fuse block 'FUSE 3X32' and text cluster 067 for SPD.</t>
         </is>
       </c>
     </row>
@@ -1180,14 +1174,14 @@
       <c r="A9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>MCCB</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>RCCB</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>MCCB 400AF</t>
+          <t>ISOL.S.+RCD</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1197,7 +1191,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>250A</t>
+          <t>16A</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1207,12 +1201,12 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>50kA</t>
+          <t>6kA</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>300mA</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -1222,16 +1216,16 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>GEN 200kVA</t>
+          <t>Lighting Group RCDs</t>
         </is>
       </c>
       <c r="L9" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
@@ -1240,7 +1234,7 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr">
@@ -1250,7 +1244,7 @@
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>Generator protection. Text 'AF=400A AT=250A'. Cable '4x150mm2'.</t>
+          <t>Group RCCBs for lighting rows from clusters 011/013 and 210/212.</t>
         </is>
       </c>
     </row>
@@ -1258,14 +1252,14 @@
       <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>MCCB</t>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>RCCB</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>MCCB 160AF</t>
+          <t>ISOL.S.+RCD</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1275,7 +1269,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>25A</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1285,12 +1279,12 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>50kA</t>
+          <t>6kA</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30mA</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1305,11 +1299,11 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>GEN 100kVA</t>
+          <t>Socket Group RCDs</t>
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
@@ -1318,7 +1312,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -1328,7 +1322,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Generator protection. Text 'AF=160A AT=125A'.</t>
+          <t>Group RCCBs for socket rows from clusters 046/048 and 219/221.</t>
         </is>
       </c>
     </row>
@@ -1336,24 +1330,24 @@
       <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>MCCB</t>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>MCB</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>MCCB 400AF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>4P</t>
+          <t>1P+N</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>250A</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1363,7 +1357,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>36kA</t>
+          <t>6kA</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1378,25 +1372,25 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Totalizing Switchboard Outgoing</t>
+          <t>Lighting - Maids Room 1/Living Room, Lighting - Maids Room 2, Lighting - Laundry Room/Storage, Lighting - Corridor, Lighting - Cold Room/Electrical Room/Solar, Lighting - Art Work/Storage, Lighting - Kids Playroom/Gym, Lighting - Kitchenette/Bathrooms, Lighting - Guest Area/Bathroom, Lighting - Guest Bedroom/Bathroom, Lighting - Technical Room, Lighting - Bathrooms, Lighting - Mechanical Room, Lighting - Parking, Spare L15, Spare L16</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
@@ -1406,7 +1400,7 @@
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>Main Gen Bus output to ATS-1. Text 'AF=400A AT=250A'.</t>
+          <t>Summed 10A lighting MCBs (L1-L16). Breaking capacity from global note.</t>
         </is>
       </c>
     </row>
@@ -1414,24 +1408,24 @@
       <c r="A12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>MCCB</t>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>MCB</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>MCCB 160AF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>4P</t>
+          <t>1P+N</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>150A</t>
+          <t>16A</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1441,7 +1435,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>36kA</t>
+          <t>6kA</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1456,25 +1450,25 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Generator Subscription</t>
+          <t>Sockets - Corridor/Coldroom/Storage, Sockets - Art Work/Storage, Sockets - Kids Playroom, Sockets - Guest Area/Bathroom, Sockets - corridor/storage/bathroom, Sockets - Laundry Room/Storage, Sockets - Maids Room1/Bathroom, Spare R8, Socket - Pool Bathroom, Socket - Spare R13, Sockets - Electrical/Mechanical/Solar Rooms, Sockets - Parking</t>
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1484,7 +1478,7 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Text 'AF=160A AT=150A'. Cable '4x70mm2'.</t>
+          <t>Summed 16A socket MCBs (R1-R9, R13-R15). R8 is a spare but listed as a 16A breaker.</t>
         </is>
       </c>
     </row>
@@ -1492,24 +1486,24 @@
       <c r="A13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>MCCB</t>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>MCB</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>MCCB 80AF</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>4P</t>
+          <t>1P+N</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>70A</t>
+          <t>20A</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1519,7 +1513,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>36kA</t>
+          <t>6kA</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1534,20 +1528,20 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Socket - Technical Room, Socket - Kitchen Appliance (R11), Socket - Kitchen Appliance (R12)</t>
         </is>
       </c>
       <c r="L13" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
@@ -1562,397 +1556,7 @@
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>Text 'AF=80A AT=70A'. Cable '4x25mm2'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>SWITCH</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Isolator Switch (IS)</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>4P</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>250A</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>ATS Source Isolation</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>BOTH</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>Located at inputs of ATS-1, ATS-2, ATS-3. Text 'IS' and '4x250A'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>SWITCH</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Manual Transfer Switch (MTS)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>4P</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>250A</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>ATS Bypass</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>BOTH</t>
-        </is>
-      </c>
-      <c r="P15" s="9" t="inlineStr">
-        <is>
-          <t>Bypass switches for ATS units. Text 'MTS1', 'MTS2' with '4x250A'. Counted as discrete switches per text labels.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>SPD</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Surge Arrestor</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>4P</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Class B&amp;C</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>ATS-1 Output, ATS-2 Output</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>DXF_ONLY</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>Text 'SURGE ARRESTOR CLASS B&amp;C'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>METER</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Digital Power Meter</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>4P</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>ATS-1, ATS-2, ATS-3 Output Analysis</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>DXF_ONLY</t>
-        </is>
-      </c>
-      <c r="P17" s="9" t="inlineStr">
-        <is>
-          <t>Text 'DIGITAL POWER METER' at outputs of all 3 ATS units.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Phase Relay</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>Main Output Protection</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>DXF_ONLY</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>Text 'PHASE RELAY' at final output to MDB. Associated cable 4x150mm feeding MDB.</t>
+          <t>R10, R11, R12 identified as 20A with 4mm2 cable from clusters 214, 222, 234.</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1985,14 +1589,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Terminal Block Schedule  ·  xyz.dwg</t>
+          <t>Terminal Block Schedule  ·  DB-B1.dwg</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Types: 1   |   Total terminals: 2</t>
+          <t>Types: 2   |   Total terminals: 31</t>
         </is>
       </c>
     </row>
@@ -2029,39 +1633,65 @@
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Terminal 70mm²+</t>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Terminal 2x2.5mm²</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Cable &gt;70mm² — check Phoenix catalog</t>
+          <t>Phoenix Contact PT 2.5 feed-through</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="E4" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Lighting - Maids Room 1/Living Room, Lighting - Maids Room 2, Lighting - Laundry Room/Storage, Lighting - Corridor, Lighting - Cold Room/Electrical Room/Solar, Lighting - Art Work/Storage, Lighting - Kids Playroom/Gym, Lighting - Kitchenette/Bathrooms, Lighting - Guest Area/Bathroom, Lighting - Guest Bedroom/Bathroom, Lighting - Technical Room, Lighting - Bathrooms, Lighting - Mechanical Room, Lighting - Parking, Spare L15, Spare L16 10A @2.5mm² | Sockets - Corridor/Coldroom/Storage, Sockets - Art Work/Storage, Sockets - Kids Playroom, Sockets - Guest Area/Bathroom, Sockets - corridor/storage/bathroom, Sockets - Laundry Room/Storage, Sockets - Maids Room1/Bathroom, Spare R8, Socket - Pool Bathroom, Socket - Spare R13, Sockets - Electrical/Mechanical/Solar Rooms, Sockets - Parking 16A @2.5mm²</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Main Output Protection - @150.0mm²</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="D5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Terminal 2x4mm²</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Phoenix Contact PT 4 feed-through</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>Socket - Technical Room, Socket - Kitchen Appliance (R11), Socket - Kitchen Appliance (R12) 20A @4.0mm²</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>2</v>
+      <c r="E6" s="22" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2079,246 +1709,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Panel Enclosure  ·  xyz.dwg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>Panel Reference</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Enclosure Size</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>Manufacturer</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Catalog / Part Number</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>Additional Information Detected  ·  xyz.dwg</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Items detected by AI as extra useful data present in this drawing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>TITLE_BLOCK</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Project and client details from title block</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Project: KORNET EL HAMRA, Client: MRS. JESSICA &amp; MR. PATRICK TOHME, Drawing Title: ATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>Cable specifications and types identified in diagram</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>Power cables (e.g., 4x150mm2+E, 4x35mm2), Control cables (2x6mm2, 4x2.5mm2), CAT6 Data cables</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>System power sources identified</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Generators (100kVA, 200kVA), EDL (Utility), Solar PV System</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>Control components mentioned</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>PLC, Phase Failure Relays (PFR), Contactors, Totalizing Switchboard</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Drawing Render  ·  xyz.dwg</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Drawing Render  ·  DB-B1.dwg</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Full DXF render from the client's drawing file.</t>
         </is>
@@ -2334,13 +1736,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2356,98 +1758,111 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>Groups</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>Total Units</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="inlineStr">
-        <is>
-          <t>CONTACTOR</t>
-        </is>
-      </c>
-      <c r="B3" s="28" t="n">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>FUSE_HOLDER</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="28" t="n">
-        <v>8</v>
+      <c r="C3" s="27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>MCCB</t>
-        </is>
-      </c>
-      <c r="B4" s="28" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" s="28" t="n">
-        <v>8</v>
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>MCB</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>METER</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>PILOT_LAMP</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>RCCB</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="28" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="B6" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="28" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="C7" s="27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>SPD</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B8" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="28" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="C8" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>SWITCH</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="28" t="n">
-        <v>12</v>
+      <c r="B9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
